--- a/data/trans_orig/IQ12A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ12A-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de días que limitaron su actividad por dolores o síntomas</t>
+          <t>Menores según el número de días que limitaron su actividad por dolores o síntomas (tasa de respuesta: 97,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 8,45</t>
+          <t>1,51; 8,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,74</t>
+          <t>1,8; 4,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 7,47</t>
+          <t>2,31; 7,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 4,64</t>
+          <t>2,87; 4,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 7,56</t>
+          <t>2,59; 7,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 8,07</t>
+          <t>2,69; 8,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,58</t>
+          <t>2,02; 4,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,5</t>
+          <t>2,31; 6,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,5</t>
+          <t>2,72; 6,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,76</t>
+          <t>2,37; 5,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,81</t>
+          <t>2,63; 6,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,01</t>
+          <t>2,87; 4,75</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,97</t>
+          <t>1,59; 3,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 6,39</t>
+          <t>3,03; 6,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,2</t>
+          <t>1,53; 3,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,94</t>
+          <t>2,2; 10,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,63</t>
+          <t>2,11; 4,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 8,37</t>
+          <t>1,5; 8,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,36</t>
+          <t>1,89; 7,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 7,78</t>
+          <t>3,08; 7,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,88</t>
+          <t>2,17; 4,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,95</t>
+          <t>2,87; 5,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,85</t>
+          <t>2,01; 5,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 7,26</t>
+          <t>3,21; 7,24</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,21</t>
+          <t>1,55; 4,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,92</t>
+          <t>1,37; 5,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 7,54</t>
+          <t>1,76; 7,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,17</t>
+          <t>2,26; 5,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,43</t>
+          <t>2,11; 5,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,27</t>
+          <t>2,48; 5,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,54</t>
+          <t>1,29; 2,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 7,47</t>
+          <t>2,26; 7,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,47</t>
+          <t>2,21; 4,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,46</t>
+          <t>2,18; 4,66</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,84</t>
+          <t>1,82; 4,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,59</t>
+          <t>2,89; 6,56</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,93</t>
+          <t>3,06; 6,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,72</t>
+          <t>2,88; 5,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,54</t>
+          <t>2,11; 3,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 6,73</t>
+          <t>4,55; 6,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,85</t>
+          <t>2,55; 6,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,28</t>
+          <t>2,21; 4,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,76</t>
+          <t>2,22; 4,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,29</t>
+          <t>4,16; 7,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,19</t>
+          <t>3,15; 5,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,63; 4,45</t>
+          <t>2,78; 4,47</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,63</t>
+          <t>2,35; 3,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 6,89</t>
+          <t>4,72; 6,79</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,97</t>
+          <t>1,55; 7,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,57</t>
+          <t>2,15; 4,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,22</t>
+          <t>2,49; 6,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 4,93</t>
+          <t>2,74; 4,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,89</t>
+          <t>2,34; 3,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,54</t>
+          <t>2,89; 6,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,42</t>
+          <t>1,69; 3,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,87</t>
+          <t>4,28; 7,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,47</t>
+          <t>2,18; 5,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,95</t>
+          <t>2,76; 4,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,79</t>
+          <t>2,39; 4,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,27</t>
+          <t>3,88; 6,21</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 11,82</t>
+          <t>1,76; 14,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,0</t>
+          <t>1,04; 4,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,71; 10,78</t>
+          <t>1,56; 10,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,55; 6,74</t>
+          <t>3,62; 6,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,69; 10,21</t>
+          <t>1,68; 10,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,45</t>
+          <t>2,53; 7,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,05; 8,93</t>
+          <t>4,01; 8,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,81; 10,6</t>
+          <t>3,95; 10,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,81; 10,25</t>
+          <t>2,84; 9,78</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,18</t>
+          <t>2,38; 6,03</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,3; 8,67</t>
+          <t>3,5; 8,96</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,36; 8,5</t>
+          <t>4,3; 8,88</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,73</t>
+          <t>2,82; 4,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,25</t>
+          <t>2,89; 4,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,68; 4,3</t>
+          <t>2,71; 4,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,73; 5,0</t>
+          <t>3,76; 5,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,05</t>
+          <t>3,18; 4,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,01; 4,51</t>
+          <t>3,03; 4,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,6; 3,93</t>
+          <t>2,57; 4,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,26</t>
+          <t>4,45; 6,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,48</t>
+          <t>3,28; 4,52</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,1</t>
+          <t>3,13; 4,09</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 3,78</t>
+          <t>2,77; 3,83</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,32; 5,52</t>
+          <t>4,37; 5,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ12A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ12A-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de días que limitaron su actividad por dolores o síntomas (tasa de respuesta: 97,76%)</t>
+          <t>Tiempo medio en días que limitaron su actividad en las últimas 2 semanas por dolores o síntomas (tasa de respuesta: 97,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,32 +716,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 8,47</t>
+          <t>1,59; 7,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,52</t>
+          <t>1,86; 4,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 7,94</t>
+          <t>2,29; 8,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,87; 4,73</t>
+          <t>2,88; 4,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 7,26</t>
+          <t>2,58; 7,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,69; 8,46</t>
+          <t>2,39; 8,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,27 +751,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,59</t>
+          <t>2,31; 6,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,64</t>
+          <t>2,7; 6,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,47</t>
+          <t>2,39; 5,28</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,94</t>
+          <t>2,55; 6,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,87; 4,75</t>
+          <t>2,86; 4,86</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,84</t>
+          <t>1,58; 3,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 6,31</t>
+          <t>3,08; 6,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,12</t>
+          <t>1,53; 3,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 10,05</t>
+          <t>2,27; 10,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,65</t>
+          <t>2,02; 4,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 8,35</t>
+          <t>1,49; 8,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,2</t>
+          <t>1,95; 7,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 7,9</t>
+          <t>3,03; 7,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,05</t>
+          <t>2,17; 3,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,91</t>
+          <t>2,77; 5,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,33</t>
+          <t>1,99; 4,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 7,24</t>
+          <t>3,18; 6,88</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,39</t>
+          <t>1,48; 4,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 5,49</t>
+          <t>1,36; 5,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,47 +1011,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,97</t>
+          <t>2,23; 5,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,42</t>
+          <t>2,21; 5,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,35</t>
+          <t>2,36; 5,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,53</t>
+          <t>1,34; 2,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 7,48</t>
+          <t>2,25; 7,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,58</t>
+          <t>2,22; 4,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,66</t>
+          <t>2,19; 4,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,97</t>
+          <t>1,81; 4,86</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,56</t>
+          <t>2,84; 6,51</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 6,0</t>
+          <t>2,96; 5,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,71</t>
+          <t>2,96; 5,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,54</t>
+          <t>2,13; 3,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,63</t>
+          <t>4,61; 6,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 6,04</t>
+          <t>2,65; 5,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,45</t>
+          <t>2,27; 4,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,89</t>
+          <t>2,24; 4,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,16; 7,19</t>
+          <t>4,24; 7,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 5,32</t>
+          <t>3,15; 5,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,47</t>
+          <t>2,83; 4,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,68</t>
+          <t>2,3; 3,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 6,79</t>
+          <t>4,72; 6,74</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 7,05</t>
+          <t>1,64; 7,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,57</t>
+          <t>2,03; 4,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,14</t>
+          <t>2,48; 6,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 4,81</t>
+          <t>2,57; 4,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,88</t>
+          <t>2,35; 3,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,79</t>
+          <t>2,82; 6,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,33</t>
+          <t>1,69; 3,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,5</t>
+          <t>4,3; 8,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,33</t>
+          <t>2,12; 5,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,88</t>
+          <t>2,75; 5,1</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,88</t>
+          <t>2,38; 4,8</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 6,21</t>
+          <t>3,87; 6,18</t>
         </is>
       </c>
     </row>
@@ -1421,57 +1421,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,31</t>
+          <t>1,24; 5,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,56; 10,72</t>
+          <t>1,71; 10,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,62; 6,97</t>
+          <t>3,73; 7,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,68; 10,47</t>
+          <t>1,62; 11,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,89</t>
+          <t>2,49; 7,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,01; 8,38</t>
+          <t>3,99; 8,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,95; 10,99</t>
+          <t>3,7; 10,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,78</t>
+          <t>2,95; 9,47</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,03</t>
+          <t>2,33; 6,24</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,5; 8,96</t>
+          <t>3,45; 8,68</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,3; 8,88</t>
+          <t>4,41; 8,64</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 4,72</t>
+          <t>2,89; 4,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,24</t>
+          <t>2,89; 4,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,21</t>
+          <t>2,63; 4,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,76; 5,08</t>
+          <t>3,75; 4,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,91</t>
+          <t>3,22; 4,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,03; 4,5</t>
+          <t>2,98; 4,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,04</t>
+          <t>2,58; 3,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,45; 6,18</t>
+          <t>4,51; 6,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,28; 4,52</t>
+          <t>3,24; 4,56</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,13; 4,09</t>
+          <t>3,14; 4,11</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 3,83</t>
+          <t>2,75; 3,78</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 5,51</t>
+          <t>4,35; 5,47</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ12A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ12A-Clase-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,56</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,62</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,31</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3,75</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3,67</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,68</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4,04</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,57</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,56</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,62</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,31</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,59</t>
+          <t>3,52</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,58</t>
+          <t>3,6</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 7,97</t>
+          <t>2,63; 7,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,53</t>
+          <t>2,45; 8,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,18</t>
+          <t>2,02; 4,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 4,72</t>
+          <t>2,33; 7,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,3</t>
+          <t>1,6; 8,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 8,01</t>
+          <t>1,86; 4,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,44</t>
+          <t>2,29; 7,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,99</t>
+          <t>2,77; 4,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,46</t>
+          <t>2,69; 6,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,28</t>
+          <t>2,53; 5,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 6,95</t>
+          <t>2,63; 6,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,86; 4,86</t>
+          <t>2,89; 5,1</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,23</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,34</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3,24</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4,68</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>2,69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,21</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,19</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,88</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,23</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,34</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,24</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,67</t>
+          <t>4,75</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,73</t>
+          <t>4,7</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,83</t>
+          <t>1,99; 4,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,35</t>
+          <t>1,49; 8,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,19</t>
+          <t>1,96; 7,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 10,1</t>
+          <t>3,07; 7,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,69</t>
+          <t>1,7; 3,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 8,31</t>
+          <t>3,04; 6,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,49</t>
+          <t>1,55; 3,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 7,72</t>
+          <t>1,95; 9,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,97</t>
+          <t>2,17; 3,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,87</t>
+          <t>2,85; 5,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,94</t>
+          <t>2,01; 4,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,88</t>
+          <t>3,3; 7,15</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,71</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,64</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,91</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4,56</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2,49</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,44</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3,41</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,24</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,71</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,64</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,91</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>4,28</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,32</t>
+          <t>4,45</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,17</t>
+          <t>2,1; 5,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,07</t>
+          <t>2,42; 5,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 7,92</t>
+          <t>1,35; 2,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,98</t>
+          <t>2,32; 7,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,41</t>
+          <t>1,47; 4,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,45</t>
+          <t>1,39; 4,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,56</t>
+          <t>1,67; 7,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 7,72</t>
+          <t>2,27; 6,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,53</t>
+          <t>2,22; 4,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,37</t>
+          <t>2,14; 4,46</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,86</t>
+          <t>1,8; 4,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 6,51</t>
+          <t>2,87; 6,93</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,78</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3,0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5,87</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4,31</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4,07</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2,68</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,75</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,78</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,0</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,13</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>5,76</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>5,83</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 5,69</t>
+          <t>2,58; 5,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 5,79</t>
+          <t>2,19; 4,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,54</t>
+          <t>2,18; 4,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 6,65</t>
+          <t>4,34; 7,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,78</t>
+          <t>2,86; 5,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,43</t>
+          <t>2,91; 5,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,62</t>
+          <t>2,16; 3,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 7,2</t>
+          <t>4,57; 6,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 5,28</t>
+          <t>3,13; 5,19</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,55</t>
+          <t>2,63; 4,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 3,69</t>
+          <t>2,32; 3,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 6,74</t>
+          <t>4,78; 6,94</t>
         </is>
       </c>
     </row>
@@ -1208,54 +1208,54 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,11</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4,25</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,39</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5,89</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>3,13</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>3,18</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>3,8</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3,61</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3,12</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>3,67</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,11</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,25</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,39</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>5,84</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>3,12</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>3,67</t>
-        </is>
-      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
           <t>3,21</t>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>4,83</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 7,13</t>
+          <t>2,24; 3,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,56</t>
+          <t>2,88; 6,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,46</t>
+          <t>1,72; 3,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,83</t>
+          <t>4,31; 7,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,99</t>
+          <t>1,64; 6,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,51</t>
+          <t>2,2; 4,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,36</t>
+          <t>2,47; 6,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,3; 8,02</t>
+          <t>2,63; 4,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,28</t>
+          <t>2,14; 5,47</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,1</t>
+          <t>2,76; 4,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,8</t>
+          <t>2,37; 4,79</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,87; 6,18</t>
+          <t>3,81; 6,31</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5,78</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4,51</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6,77</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7,05</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>5,67</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2,38</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4,73</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4,98</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,78</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,51</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6,77</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,92</t>
+          <t>4,88</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,97</t>
+          <t>5,96</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 14,0</t>
+          <t>1,69; 10,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>2,39; 7,45</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4,05; 8,93</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>3,82; 10,83</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1,76; 11,82</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>1,24; 5,0</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1,71; 10,68</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>3,73; 7,29</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>1,62; 11,77</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>2,49; 7,68</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,99; 8,38</t>
+          <t>1,71; 10,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,7; 10,75</t>
+          <t>3,44; 6,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,95; 9,47</t>
+          <t>2,81; 10,25</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,24</t>
+          <t>2,49; 6,18</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,45; 8,68</t>
+          <t>3,3; 8,67</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,41; 8,64</t>
+          <t>4,26; 8,52</t>
         </is>
       </c>
     </row>
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,95</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3,68</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,17</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5,42</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>3,67</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>3,46</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>3,29</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,32</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,95</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,68</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,17</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,32</t>
+          <t>4,26</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,88</t>
+          <t>4,9</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,69</t>
+          <t>3,22; 5,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,23</t>
+          <t>3,01; 4,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 4,21</t>
+          <t>2,6; 3,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,75; 4,95</t>
+          <t>4,58; 6,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,22; 4,91</t>
+          <t>2,83; 4,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,5</t>
+          <t>2,89; 4,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 3,98</t>
+          <t>2,68; 4,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,19</t>
+          <t>3,66; 4,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,24; 4,56</t>
+          <t>3,25; 4,48</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,11</t>
+          <t>3,14; 4,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,75; 3,78</t>
+          <t>2,79; 3,78</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,35; 5,47</t>
+          <t>4,33; 5,54</t>
         </is>
       </c>
     </row>
